--- a/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536128_LIGAREGULARA_PROCESSED.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/individual/NP_play_by_play_2536128_LIGAREGULARA_PROCESSED.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y26"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1621,7 +1621,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. SANCHES CARDOSO MENDES</t>
+          <t>D. RAMIREZ SANCHEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1633,67 +1633,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5715</v>
+        <v>1.725</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1851</v>
+        <v>3.8803</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6135</v>
+        <v>-2.1553</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9314</v>
+        <v>-0.09859999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>2.438</v>
+        <v>0.4345</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.5066</v>
+        <v>-0.5331</v>
       </c>
       <c r="J15" t="n">
-        <v>4.1178</v>
+        <v>3.3617</v>
       </c>
       <c r="K15" t="n">
-        <v>3.8748</v>
+        <v>2.0091</v>
       </c>
       <c r="L15" t="n">
-        <v>0.243</v>
+        <v>1.3526</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.1864</v>
+        <v>-3.4603</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.4368</v>
+        <v>-1.5746</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.7496</v>
+        <v>-1.8857</v>
       </c>
       <c r="P15" t="n">
-        <v>0.585</v>
+        <v>1.3649</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9499</v>
+        <v>-0.9749</v>
       </c>
       <c r="R15" t="n">
-        <v>2.5348</v>
+        <v>2.3398</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3337</v>
+        <v>0.4587</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0171</v>
+        <v>-0.0051</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3166</v>
+        <v>0.4638</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2786</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.4986</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2786</v>
+        <v>-1.4986</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. RAMIREZ SANCHEZ</t>
+          <t>R. SANCHES CARDOSO MENDES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1716,67 +1716,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4175</v>
+        <v>1.5715</v>
       </c>
       <c r="E16" t="n">
-        <v>3.5728</v>
+        <v>2.1851</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.1553</v>
+        <v>-0.6135</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4061</v>
+        <v>0.9314</v>
       </c>
       <c r="H16" t="n">
-        <v>0.127</v>
+        <v>2.438</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5331</v>
+        <v>-1.5066</v>
       </c>
       <c r="J16" t="n">
-        <v>3.0542</v>
+        <v>4.1178</v>
       </c>
       <c r="K16" t="n">
-        <v>1.7016</v>
+        <v>3.8748</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3526</v>
+        <v>0.243</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.4603</v>
+        <v>-3.1864</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.5746</v>
+        <v>-1.4368</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.8857</v>
+        <v>-1.7496</v>
       </c>
       <c r="P16" t="n">
-        <v>1.3649</v>
+        <v>0.585</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9749</v>
+        <v>-1.9499</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3398</v>
+        <v>2.5348</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4587</v>
+        <v>0.3337</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0051</v>
+        <v>0.0171</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4638</v>
+        <v>0.3166</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.2786</v>
       </c>
       <c r="W16" t="n">
-        <v>1.4986</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.4986</v>
+        <v>-0.2786</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. RAMÍREZ SÁNCHEZ</t>
+          <t>B. EDOKPAYI MANCERA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1799,67 +1799,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3075</v>
+        <v>0.214</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3075</v>
+        <v>1.4685</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>-1.2545</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3075</v>
+        <v>1.4457</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3075</v>
+        <v>-1.0216</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>2.4673</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3075</v>
+        <v>2.7987</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3075</v>
+        <v>-0.336</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3.1346</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>-1.353</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-0.6857</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-0.6673</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.3398</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.3398</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-0.4684</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>-0.6673</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.1989</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-3.1031</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.6629</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-2.4401</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B. EDOKPAYI MANCERA</t>
+          <t>A. DIAZ ROLLANO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1882,67 +1882,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.214</v>
+        <v>-0.6523</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4685</v>
+        <v>-0.1795</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2545</v>
+        <v>-0.4728</v>
       </c>
       <c r="G18" t="n">
-        <v>1.4457</v>
+        <v>-1.4467</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0216</v>
+        <v>-0.2364</v>
       </c>
       <c r="I18" t="n">
-        <v>2.4673</v>
+        <v>-1.2103</v>
       </c>
       <c r="J18" t="n">
-        <v>2.7987</v>
+        <v>0.1131</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.336</v>
+        <v>0.656</v>
       </c>
       <c r="L18" t="n">
-        <v>3.1346</v>
+        <v>-0.543</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.353</v>
+        <v>-1.5598</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6857</v>
+        <v>-0.8924</v>
       </c>
       <c r="O18" t="n">
         <v>-0.6673</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3398</v>
+        <v>0.7799</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9749</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3398</v>
+        <v>1.7549</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4684</v>
+        <v>0.0145</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6673</v>
+        <v>-0.5377</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1989</v>
+        <v>0.5521</v>
       </c>
       <c r="V18" t="n">
-        <v>-3.1031</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6629</v>
+        <v>1.2201</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.4401</v>
+        <v>-1.2201</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. DIAZ ROLLANO</t>
+          <t>A. ARTILES AGUILAR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1965,67 +1965,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6523</v>
+        <v>-1.0123</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1795</v>
+        <v>-2.3252</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4728</v>
+        <v>1.3128</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.4467</v>
+        <v>-1.1709</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2364</v>
+        <v>0.127</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2103</v>
+        <v>-1.2979</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1131</v>
+        <v>-0.628</v>
       </c>
       <c r="K19" t="n">
-        <v>0.656</v>
+        <v>0.6765</v>
       </c>
       <c r="L19" t="n">
+        <v>-1.3045</v>
+      </c>
+      <c r="M19" t="n">
         <v>-0.543</v>
       </c>
-      <c r="M19" t="n">
-        <v>-1.5598</v>
-      </c>
       <c r="N19" t="n">
-        <v>-0.8924</v>
+        <v>-0.5496</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6673</v>
+        <v>0.0066</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7799</v>
+        <v>0.585</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9749</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7549</v>
+        <v>1.5599</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0145</v>
+        <v>-0.4793</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5377</v>
+        <v>-0.7223000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5521</v>
+        <v>0.243</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.0529</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2201</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2201</v>
+        <v>0.0529</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. ARTILES AGUILAR</t>
+          <t>R. REID</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2048,67 +2048,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0123</v>
+        <v>-1.3058</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.3252</v>
+        <v>-0.6929</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3128</v>
+        <v>-0.6129</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1709</v>
+        <v>-1.0968</v>
       </c>
       <c r="H20" t="n">
-        <v>0.127</v>
+        <v>-3.5495</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.2979</v>
+        <v>2.4527</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.628</v>
+        <v>0.4006</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6765</v>
+        <v>-2.0455</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3045</v>
+        <v>2.4461</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.543</v>
+        <v>-1.4974</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5496</v>
+        <v>-1.504</v>
       </c>
       <c r="O20" t="n">
         <v>0.0066</v>
       </c>
       <c r="P20" t="n">
-        <v>0.585</v>
+        <v>-0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9749</v>
+        <v>-1.9499</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5599</v>
+        <v>1.9499</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4793</v>
+        <v>-0.209</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7223000000000001</v>
+        <v>-0.3637</v>
       </c>
       <c r="U20" t="n">
-        <v>0.243</v>
+        <v>0.1547</v>
       </c>
       <c r="V20" t="n">
-        <v>0.0529</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2201</v>
       </c>
       <c r="X20" t="n">
-        <v>0.0529</v>
+        <v>-1.2201</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. REID</t>
+          <t>T. VAN BRANDWIJK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2131,67 +2131,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3058</v>
+        <v>-1.6497</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6929</v>
+        <v>-1.9376</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6129</v>
+        <v>0.2878</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.0968</v>
+        <v>-1.7077</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.5495</v>
+        <v>-0.7324000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>2.4527</v>
+        <v>-0.9752999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4006</v>
+        <v>-1.778</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.0455</v>
+        <v>-0.66</v>
       </c>
       <c r="L21" t="n">
-        <v>2.4461</v>
+        <v>-1.118</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.4974</v>
+        <v>0.0703</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.504</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0066</v>
+        <v>0.1427</v>
       </c>
       <c r="P21" t="n">
-        <v>-0</v>
+        <v>1.3649</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9499</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9499</v>
+        <v>1.3649</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.209</v>
+        <v>0.1388</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3637</v>
+        <v>-0.1595</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1547</v>
+        <v>0.2983</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.4457</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2201</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2201</v>
+        <v>-1.4457</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>T. VAN BRANDWIJK</t>
+          <t>T. FIELDS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2214,67 +2214,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6497</v>
+        <v>-3.2735</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9376</v>
+        <v>-2.6362</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2878</v>
+        <v>-0.6373</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.7077</v>
+        <v>-3.8456</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7324000000000001</v>
+        <v>-2.4214</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9752999999999999</v>
+        <v>-1.4241</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.778</v>
+        <v>-1.202</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.66</v>
+        <v>-1.2585</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.118</v>
+        <v>0.0565</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0703</v>
+        <v>-2.6436</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.07240000000000001</v>
+        <v>-1.1629</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1427</v>
+        <v>-1.4807</v>
       </c>
       <c r="P22" t="n">
-        <v>1.3649</v>
+        <v>0.9749</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.9749</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3649</v>
+        <v>1.9499</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1388</v>
+        <v>-0.1243</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1595</v>
+        <v>-0.4592</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2983</v>
+        <v>0.335</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.4457</v>
+        <v>-0.2786</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.4457</v>
+        <v>-0.2786</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>T. FIELDS</t>
+          <t>B. GARCIA ALVAREZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2297,67 +2297,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.2735</v>
+        <v>-4.4713</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6362</v>
+        <v>-2.466</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6373</v>
+        <v>-2.0053</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.8456</v>
+        <v>-7.5387</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.4214</v>
+        <v>-2.7996</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.4241</v>
+        <v>-4.7391</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.202</v>
+        <v>-3.5355</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.2585</v>
+        <v>-0.951</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0565</v>
+        <v>-2.5845</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.6436</v>
+        <v>-4.0032</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.1629</v>
+        <v>-1.8486</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.4807</v>
+        <v>-2.1546</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9749</v>
+        <v>1.7549</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9749</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.9499</v>
+        <v>1.7549</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1243</v>
+        <v>-0.1861</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4592</v>
+        <v>-0.4291</v>
       </c>
       <c r="U23" t="n">
-        <v>0.335</v>
+        <v>0.243</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.2786</v>
+        <v>1.4986</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.4986</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2786</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B. GARCIA ALVAREZ</t>
+          <t>E. EGEA SOLER</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2380,67 +2380,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.4713</v>
+        <v>-4.7651</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.466</v>
+        <v>-3.2398</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.0053</v>
+        <v>-1.5254</v>
       </c>
       <c r="G24" t="n">
-        <v>-7.5387</v>
+        <v>-5.1757</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.7996</v>
+        <v>-2.6919</v>
       </c>
       <c r="I24" t="n">
-        <v>-4.7391</v>
+        <v>-2.4838</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.5355</v>
+        <v>-3.2111</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.951</v>
+        <v>-1.939</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.5845</v>
+        <v>-1.272</v>
       </c>
       <c r="M24" t="n">
-        <v>-4.0032</v>
+        <v>-1.9646</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.8486</v>
+        <v>-0.7529</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.1546</v>
+        <v>-1.2118</v>
       </c>
       <c r="P24" t="n">
-        <v>1.7549</v>
+        <v>1.5599</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.7549</v>
+        <v>1.5599</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1861</v>
+        <v>0.0707</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4291</v>
+        <v>-0.0287</v>
       </c>
       <c r="U24" t="n">
-        <v>0.243</v>
+        <v>0.0994</v>
       </c>
       <c r="V24" t="n">
-        <v>1.4986</v>
+        <v>-1.2201</v>
       </c>
       <c r="W24" t="n">
-        <v>1.4986</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.2201</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>E. EGEA SOLER</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2463,152 +2463,69 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.7651</v>
+        <v>-10.841</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.2398</v>
+        <v>-2.470600000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.5254</v>
+        <v>-8.370699999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.1757</v>
+        <v>-17.4326</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.6919</v>
+        <v>-13.3001</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.4838</v>
+        <v>-4.132400000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.2111</v>
+        <v>6.2981</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.939</v>
+        <v>-1.6541</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.272</v>
+        <v>7.952099999999998</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.9646</v>
+        <v>-23.7308</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.7529</v>
+        <v>-11.6462</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.2118</v>
+        <v>-12.0846</v>
       </c>
       <c r="P25" t="n">
-        <v>1.5599</v>
+        <v>11.6992</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>-9.7493</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5599</v>
+        <v>21.4485</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0707</v>
+        <v>-0.3331999999999998</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.0287</v>
+        <v>-3.7937</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0994</v>
+        <v>3.4606</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.2201</v>
+        <v>-4.7746</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>4.7745</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.2201</v>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>play_by_play_2536128_LIGAREGULARA_PROCESSED.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>CB ALGECIRAS</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="n">
-        <v>-10.841</v>
-      </c>
-      <c r="E26" t="n">
-        <v>-2.4706</v>
-      </c>
-      <c r="F26" t="n">
-        <v>-8.370699999999999</v>
-      </c>
-      <c r="G26" t="n">
-        <v>-17.4326</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-13.3001</v>
-      </c>
-      <c r="I26" t="n">
-        <v>-4.132399999999999</v>
-      </c>
-      <c r="J26" t="n">
-        <v>6.2981</v>
-      </c>
-      <c r="K26" t="n">
-        <v>-1.6541</v>
-      </c>
-      <c r="L26" t="n">
-        <v>7.9521</v>
-      </c>
-      <c r="M26" t="n">
-        <v>-23.7308</v>
-      </c>
-      <c r="N26" t="n">
-        <v>-11.6462</v>
-      </c>
-      <c r="O26" t="n">
-        <v>-12.0846</v>
-      </c>
-      <c r="P26" t="n">
-        <v>11.6992</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>-9.7493</v>
-      </c>
-      <c r="R26" t="n">
-        <v>21.4485</v>
-      </c>
-      <c r="S26" t="n">
-        <v>-0.3331999999999999</v>
-      </c>
-      <c r="T26" t="n">
-        <v>-3.793700000000001</v>
-      </c>
-      <c r="U26" t="n">
-        <v>3.4606</v>
-      </c>
-      <c r="V26" t="n">
-        <v>-4.7746</v>
-      </c>
-      <c r="W26" t="n">
-        <v>4.7745</v>
-      </c>
-      <c r="X26" t="n">
         <v>-9.549000000000001</v>
       </c>
-      <c r="Y26" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
